--- a/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar1_Q40_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar1_Q40_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001491286263478225</v>
+        <v>0.001458251495392775</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001491286263478225</v>
+        <v>0.001458251495392775</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001401608225389296</v>
+        <v>0.001643627825333411</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001407619732364193</v>
+        <v>0.001362542628289153</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001407619732364193</v>
+        <v>0.001362542628289153</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009799129398467175</v>
+        <v>0.001095769475638822</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.001714358167827744</v>
+        <v>0.001674949951973025</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001714358167827744</v>
+        <v>0.001674949951973025</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0008064117429281659</v>
+        <v>0.0007738994278572483</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.002670195659358408</v>
+        <v>0.002662144702976305</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002670195659358408</v>
+        <v>0.002662144702976305</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001277541340662092</v>
+        <v>0.001322957137287834</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0040787171907178</v>
+        <v>0.004070675271230399</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0040787171907178</v>
+        <v>0.004070675271230399</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002455981445385171</v>
+        <v>0.002748020855217608</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.005540815833783688</v>
+        <v>0.005502387748234978</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005540815833783688</v>
+        <v>0.005502387748234978</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002761131724793741</v>
+        <v>0.003046530915997361</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.007438443568333752</v>
+        <v>0.00738920846368075</v>
       </c>
       <c r="C8" t="n">
-        <v>0.007438443568333752</v>
+        <v>0.00738920846368075</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003087118424739987</v>
+        <v>0.003321731997602103</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.009255844319015246</v>
+        <v>0.009217312216882172</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009255844319015246</v>
+        <v>0.009217312216882172</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003804532466220228</v>
+        <v>0.004144998042976935</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.01050103720744624</v>
+        <v>0.01046707057050343</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01050103720744624</v>
+        <v>0.01046707057050343</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00441078337050072</v>
+        <v>0.004847351736455856</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01106677346288572</v>
+        <v>0.01102149272967794</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01106677346288572</v>
+        <v>0.01102149272967794</v>
       </c>
       <c r="D11" t="n">
-        <v>0.004714186288058197</v>
+        <v>0.005189430424057304</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01098495490049518</v>
+        <v>0.01092450985820428</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01098495490049518</v>
+        <v>0.01092450985820428</v>
       </c>
       <c r="D12" t="n">
-        <v>0.004731224527335491</v>
+        <v>0.005192126186238595</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01061104091916693</v>
+        <v>0.0105462409471927</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01061104091916693</v>
+        <v>0.0105462409471927</v>
       </c>
       <c r="D13" t="n">
-        <v>0.004551645994639889</v>
+        <v>0.005005090792738171</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01011964373937037</v>
+        <v>0.0100622490982422</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01011964373937037</v>
+        <v>0.0100622490982422</v>
       </c>
       <c r="D14" t="n">
-        <v>0.004311072701636318</v>
+        <v>0.004778036348660807</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.009434823073039623</v>
+        <v>0.009385282674220112</v>
       </c>
       <c r="C15" t="n">
-        <v>0.009434823073039623</v>
+        <v>0.009385282674220112</v>
       </c>
       <c r="D15" t="n">
-        <v>0.004050970549657137</v>
+        <v>0.004502152159442122</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.009165965900040655</v>
+        <v>0.00912515713102079</v>
       </c>
       <c r="C16" t="n">
-        <v>0.009165965900040655</v>
+        <v>0.00912515713102079</v>
       </c>
       <c r="D16" t="n">
-        <v>0.003887808942296299</v>
+        <v>0.00439063615706513</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.008579821119541911</v>
+        <v>0.008547073828411991</v>
       </c>
       <c r="C17" t="n">
-        <v>0.008579821119541911</v>
+        <v>0.008547073828411991</v>
       </c>
       <c r="D17" t="n">
-        <v>0.00366203162877057</v>
+        <v>0.004193159994582361</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.008189220287668319</v>
+        <v>0.008164443982974673</v>
       </c>
       <c r="C18" t="n">
-        <v>0.008189220287668319</v>
+        <v>0.008164443982974673</v>
       </c>
       <c r="D18" t="n">
-        <v>0.003525970833939179</v>
+        <v>0.004069213349312553</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.008316121627252119</v>
+        <v>0.008294859168304467</v>
       </c>
       <c r="C19" t="n">
-        <v>0.008316121627252119</v>
+        <v>0.008294859168304467</v>
       </c>
       <c r="D19" t="n">
-        <v>0.003414422994247977</v>
+        <v>0.003949715345024927</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.007759023518301793</v>
+        <v>0.007745143236017478</v>
       </c>
       <c r="C20" t="n">
-        <v>0.007759023518301793</v>
+        <v>0.007745143236017478</v>
       </c>
       <c r="D20" t="n">
-        <v>0.003397419924990023</v>
+        <v>0.003889854197044561</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.007523747307618763</v>
+        <v>0.007535395177079855</v>
       </c>
       <c r="C21" t="n">
-        <v>0.007523747307618763</v>
+        <v>0.007535395177079855</v>
       </c>
       <c r="D21" t="n">
-        <v>0.003244427397927018</v>
+        <v>0.003774780788368854</v>
       </c>
     </row>
   </sheetData>
